--- a/SGI_Sistema-de-gestao-integrado/SGA_Sistema-de-gestao-ambiental/Registos_SGA_Plasticom/SGA-03_Aspetos_Impactes_Ambientais.xlsx
+++ b/SGI_Sistema-de-gestao-integrado/SGA_Sistema-de-gestao-ambiental/Registos_SGA_Plasticom/SGA-03_Aspetos_Impactes_Ambientais.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project Portfolios\manufacturing-performance-analytics\SGI_Sistema-de-gestao-integrado\SGA_Sistema-de-gestao-ambiental\Registos_SGA_Plasticom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9933431-27B7-41B6-8A2E-5CB405F4097D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF4A99B6-2E79-4258-8E05-06F5824C6441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1495,7 +1495,7 @@
     <t>Injeção de tampas</t>
   </si>
   <si>
-    <t>Moldação por injeção (IM-001 a IM-008)</t>
+    <t>Moldação por injeção (IM-001 a IM-009)</t>
   </si>
   <si>
     <t>Consumo de energia elétrica (aquecimento do canhão, hidráulica, extração)</t>
@@ -14223,7 +14223,7 @@
     <row r="13" spans="1:33" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="24" t="str">
         <f>INDEX(Aspetos_Impactes!$C$5:$C$47,7)&amp;" — "&amp;INDEX(Aspetos_Impactes!$D$5:$D$47,7)</f>
-        <v>Injeção de tampas — Moldação por injeção (IM-001 a IM-008)</v>
+        <v>Injeção de tampas — Moldação por injeção (IM-001 a IM-009)</v>
       </c>
       <c r="B13" s="24" t="str">
         <f>INDEX(Aspetos_Impactes!$A$5:$A$47,7)</f>
@@ -14357,7 +14357,7 @@
     <row r="14" spans="1:33" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="24" t="str">
         <f>INDEX(Aspetos_Impactes!$C$5:$C$47,8)&amp;" — "&amp;INDEX(Aspetos_Impactes!$D$5:$D$47,8)</f>
-        <v>Injeção de tampas — Moldação por injeção (IM-001 a IM-008)</v>
+        <v>Injeção de tampas — Moldação por injeção (IM-001 a IM-009)</v>
       </c>
       <c r="B14" s="24" t="str">
         <f>INDEX(Aspetos_Impactes!$A$5:$A$47,8)</f>
